--- a/VerveStacks_THA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_THA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_THA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA9D7A5-C076-4786-8C7E-FA4FB505781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F41146A-274F-4C91-AB3E-B66AFEC887A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4114,7 +4114,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5270C5C-4151-4774-9D33-8F24ABDA4F04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCE1004-E7CB-4261-8A10-A90C4BFA5D53}">
   <dimension ref="B2:AF673"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17747,7 +17747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6AB7329-86F0-4482-881F-607927BFA9DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776789B6-7E54-43AE-BAB0-BBECAC9AACC3}">
   <dimension ref="B9:L14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
